--- a/publiclogic/canon/PublicLogic_PuddleJumper_Runtime.xlsx
+++ b/publiclogic/canon/PublicLogic_PuddleJumper_Runtime.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canon Registry" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canon Collisions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxonomy" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Vocabulary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Envelope" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artifact Registry" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PJ Event Log" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal Intake" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Queue" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumers" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Overview" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Next Steps" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Architecture" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Canon Registry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Canon Collisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Control" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Taxonomy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Event Vocabulary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Event Envelope" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Artifact Registry" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PJ Event Log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Signal Intake" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Review Queue" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Sources" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Consumers" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Validation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Case Overview" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Intake" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Documents" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Decisions" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Next Steps" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="LaneList">Control!$B$14:$B$17</definedName>
@@ -11706,12 +11706,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>This workbook</t>
+          <t>puddlejumper/apps/puddlejumper/src/archieve/event-catalog.ts</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Event Vocabulary sheet</t>
+          <t>ArchieveEventType</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Workbook</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LogicOS Build Spec v3 (SQLite CHECK)</t>
+          <t>This workbook (governance vocabulary; no runtime enforces it)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Workbook</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">

--- a/publiclogic/canon/PublicLogic_PuddleJumper_Runtime.xlsx
+++ b/publiclogic/canon/PublicLogic_PuddleJumper_Runtime.xlsx
@@ -56,6 +56,7 @@
     <definedName name="SensitivityList">Control!$Y$14:$Y$17</definedName>
     <definedName name="ObjectTypeList">Control!$Z$14:$Z$19</definedName>
     <definedName name="ReviewThreshold">Control!$B$55</definedName>
+    <definedName name="EventFamilyList">Control!$AA$14:$AA$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11100,7 +11101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -11692,7 +11693,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Event Type</t>
+          <t>Artifact Event</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11706,12 +11707,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>puddlejumper/apps/puddlejumper/src/archieve/event-catalog.ts</t>
+          <t>This workbook (Event Vocabulary sheet)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ArchieveEventType</t>
+          <t>Closed Event Vocabulary</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -11723,7 +11724,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Workbook</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -12070,322 +12071,361 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Event Family</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EventFamilyList</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>COUNTA(EventFamilyList)</f>
+        <v/>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>golden-path/src/audit.js</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AUDIT_EVENT_FAMILIES</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <f>IF(AND(C23=F23,OR(J23="n/a",J23="OK"),K23="OK"),"OK","DRIFT")</f>
+        <v/>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>process; transition; role; auth; divergence; system</t>
+        </is>
+      </c>
+      <c r="J23">
+        <f>IF(SUMPRODUCT(--EXACT(EventFamilyList,{"process";"transition";"role";"auth";"divergence";"system"}))=6,"OK","DRIFT")</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>IF(COUNTA(Control!$AA$20:$AA$24)=0,"OK","SPILL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARCHIEVE Event Family Map</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>puddlejumper canon.json (ArchieveEventTypeValue -&gt; AuditEventFamily)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ARCHIEVE_EVENT_FAMILY</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>UNVERIFIABLE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Code (puddlejumper)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>cross-repo — human-approved map, revision-pinned</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>DERIVED VIEWS — may cite canon, may never define it</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>May define</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Must cite</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Drift risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PublicLogic_Website_Workbook_FINAL_LOCKED.xlsx</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Brand, pricing, hero copy</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>VAULT wording; "runtime not engine"</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>High — asserts canon it does not own</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Move Forward — v1 Business Stack.docx</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Offer ladder, tiers, 90-day plan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nothing operational</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Capabilities &amp; Opportunity Brief (Timber Logistics)</t>
+          <t>PublicLogic_Website_Workbook_FINAL_LOCKED.xlsx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Client-specific findings</t>
+          <t>Brand, pricing, hero copy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VAULT; Claim Status vocabulary</t>
+          <t>VAULT wording; "runtime not engine"</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Medium — originated Claim Status; now canon here</t>
+          <t>High — asserts canon it does not own</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>github.com/97n8/lab · packages/golden-path</t>
+          <t>Move Forward — v1 Business Stack.docx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Runtime-enforced vocabularies (see above)</t>
+          <t>Offer ladder, tiers, 90-day plan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nothing — this IS canon for those</t>
+          <t>Nothing operational</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>None. Code is canon.</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>github.com/97n8/lab · publiclogic web</t>
+          <t>Capabilities &amp; Opportunity Brief (Timber Logistics)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Site structure, SEO, routes</t>
+          <t>Client-specific findings</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brand + canon guardrails from the Website Workbook</t>
+          <t>VAULT; Claim Status vocabulary</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Medium — README restates canon inline</t>
+          <t>Medium — originated Claim Status; now canon here</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>github.com/97n8/lab · packages/golden-path</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Runtime-enforced vocabularies (see above)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nothing — this IS canon for those</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>None. Code is canon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>github.com/97n8/lab · publiclogic web</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Site structure, SEO, routes</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brand + canon guardrails from the Website Workbook</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Medium — README restates canon inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>github.com/97n8/puddlejumper (private)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Unknown — not auditable from here</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Everything above</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Unassessed</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Open question: PJ's own product artifacts (e.g. the Event Envelope) have no lane in LOCKED_LANES. They are mapped to PROJECT here. Either add a PRODUCT lane in code or accept the mapping — but decide, and record the decision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>SUPERSEDED</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LogicOS Master Build Spec v3.0 (Apr 2026)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Nothing — brand retired</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Object model, hierarchy, enforcement boundary, sensitivity survive; harvested into canon</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>High — names LogicOS as product and PJ as backend control plane. Both false now.</t>
+          <t>Open question: PJ's own product artifacts (e.g. the Event Envelope) have no lane in LOCKED_LANES. They are mapped to PROJECT here. Either add a PRODUCT lane in code or accept the mapping — but decide, and record the decision.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LogicOS / LogicDash / LogicSuite / Syncronate</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Retired names</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Do not reintroduce</t>
-        </is>
-      </c>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>LogicOS Master Build Spec v3.0 (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nothing — brand retired</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Object model, hierarchy, enforcement boundary, sensitivity survive; harvested into canon</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>High — names LogicOS as product and PJ as backend control plane. Both false now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LogicOS / LogicDash / LogicSuite / Syncronate</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Retired names</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Do not reintroduce</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>governanceEngine, chainStore</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Nothing</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Retired — and "engine" violates canon</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Runtime, never engine</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>DERIVED VIEWS — batch 2</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>VAULT Master Build Spec v0.02</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>VAULT doctrine</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CRITICAL — redefines VAULT with different pillars</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SYNCHRON8 Build Spec v1.1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Everything</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CRITICAL — "engine"; depends on prohibited n8n + killed AXIS</t>
-        </is>
-      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LOGICBRIDGE Build Spec v1.0</t>
+          <t>VAULT Master Build Spec v0.02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12395,19 +12435,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Connector contract</t>
+          <t>VAULT doctrine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HIGH — superseded by golden-path connector.js</t>
+          <t>CRITICAL — redefines VAULT with different pillars</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PuddleJumper Build Spec v1.0</t>
+          <t>SYNCHRON8 Build Spec v1.1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12417,41 +12457,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PJ identity</t>
+          <t>Everything</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRITICAL — subordinates PJ to LogicSuite</t>
+          <t>CRITICAL — "engine"; depends on prohibited n8n + killed AXIS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vocabularies occupy Control rows 14-28. Doctrine prose begins at row 29 and must never be written into a vocabulary column above it. The spill guard watches the five rows below each named range.</t>
+          <t>LOGICBRIDGE Build Spec v1.0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PJ single-brand rule (keep this)</t>
+          <t>Nothing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PJ identity</t>
+          <t>Connector contract</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HIGH — "Workflow Engine"</t>
+          <t>HIGH — superseded by golden-path connector.js</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LogicOS Ecosystem Spec v2.0</t>
+          <t>PuddleJumper Build Spec v1.0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12461,76 +12501,120 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Everything</t>
+          <t>PJ identity</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SUPERSEDED — brand retired</t>
+          <t>CRITICAL — subordinates PJ to LogicSuite</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PublicLogic Canon 5-Page v1.0</t>
+          <t>Vocabularies occupy Control rows 14-28. Doctrine prose begins at row 29 and must never be written into a vocabulary column above it. The spill guard watches the five rows below each named range.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Positioning, COPEC, offer prices</t>
+          <t>PJ single-brand rule (keep this)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Product definitions</t>
+          <t>PJ identity</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRITICAL — redefines VAULT, ARCHIEVE, PJ; uses "engine"</t>
+          <t>HIGH — "Workflow Engine"</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cyclical Services Model v1.0</t>
+          <t>LogicOS Ecosystem Spec v2.0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cycle, funding mechanism, cost treatment</t>
+          <t>Nothing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VAULT, CaseSpace</t>
+          <t>Everything</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>SUPERSEDED — brand retired</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>PublicLogic Canon 5-Page v1.0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Positioning, COPEC, offer prices</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Product definitions</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CRITICAL — redefines VAULT, ARCHIEVE, PJ; uses "engine"</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cyclical Services Model v1.0</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cycle, funding mechanism, cost treatment</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VAULT, CaseSpace</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Erving 90-Day Framework v6</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Nothing product-related</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Nothing</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>None — not canon</t>
         </is>
@@ -13564,7 +13648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48.13000106811523" customWidth="1" min="1" max="1"/>
@@ -13826,6 +13910,11 @@
           <t>ObjectType</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>EventFamilies</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13958,6 +14047,11 @@
           <t>Record</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14085,6 +14179,11 @@
           <t>Case</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>transition</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14197,6 +14296,11 @@
           <t>Task</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -14284,6 +14388,11 @@
           <t>OrgNode</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="E18" t="inlineStr">
@@ -14331,6 +14440,11 @@
           <t>Alert</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>divergence</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="E19" t="inlineStr">
@@ -14371,6 +14485,11 @@
       <c r="Z19" t="inlineStr">
         <is>
           <t>EvidencePackage</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>system</t>
         </is>
       </c>
     </row>
